--- a/Backtest/05-01-24/S&P500stock_05-01-24period252RS90.xlsx
+++ b/Backtest/05-01-24/S&P500stock_05-01-24period252RS90.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="70">
   <si>
     <t>Stock</t>
   </si>
@@ -127,154 +127,103 @@
     <t>EM Rating</t>
   </si>
   <si>
-    <t>KKR</t>
-  </si>
-  <si>
-    <t>CRM</t>
-  </si>
-  <si>
-    <t>PANW</t>
-  </si>
-  <si>
-    <t>ABNB</t>
+    <t>GDDY</t>
+  </si>
+  <si>
+    <t>PGR</t>
   </si>
   <si>
     <t>NVDA</t>
   </si>
   <si>
-    <t>AMZN</t>
-  </si>
-  <si>
-    <t>VST</t>
-  </si>
-  <si>
-    <t>NOW</t>
-  </si>
-  <si>
-    <t>RCL</t>
-  </si>
-  <si>
-    <t>CRWD</t>
-  </si>
-  <si>
-    <t>CCL</t>
-  </si>
-  <si>
-    <t>WDAY</t>
-  </si>
-  <si>
-    <t>BKNG</t>
-  </si>
-  <si>
-    <t>TDG</t>
-  </si>
-  <si>
-    <t>EXPE</t>
+    <t>PWR</t>
+  </si>
+  <si>
+    <t>WAB</t>
   </si>
   <si>
     <t>PH</t>
   </si>
   <si>
-    <t>CMG</t>
-  </si>
-  <si>
     <t>DELL</t>
   </si>
   <si>
-    <t>ANET</t>
-  </si>
-  <si>
-    <t>inf</t>
-  </si>
-  <si>
-    <t>2024-02-06</t>
-  </si>
-  <si>
-    <t>2024-02-28</t>
-  </si>
-  <si>
-    <t>2024-02-20</t>
-  </si>
-  <si>
-    <t>2024-02-13</t>
-  </si>
-  <si>
-    <t>2024-02-21</t>
-  </si>
-  <si>
-    <t>2024-02-01</t>
-  </si>
-  <si>
-    <t>2024-01-24</t>
-  </si>
-  <si>
-    <t>2024-03-05</t>
-  </si>
-  <si>
-    <t>2024-03-27</t>
-  </si>
-  <si>
-    <t>2024-02-26</t>
-  </si>
-  <si>
-    <t>2024-02-22</t>
-  </si>
-  <si>
-    <t>2024-02-08</t>
-  </si>
-  <si>
-    <t>2024-02-29</t>
-  </si>
-  <si>
-    <t>2024-02-12</t>
+    <t>GOOGL</t>
+  </si>
+  <si>
+    <t>GOOG</t>
+  </si>
+  <si>
+    <t>IR</t>
+  </si>
+  <si>
+    <t>ETN</t>
+  </si>
+  <si>
+    <t>DVA</t>
+  </si>
+  <si>
+    <t>2024-05-02</t>
+  </si>
+  <si>
+    <t>2024-07-16</t>
+  </si>
+  <si>
+    <t>2024-05-22</t>
+  </si>
+  <si>
+    <t>2024-07-24</t>
+  </si>
+  <si>
+    <t>2024-05-30</t>
+  </si>
+  <si>
+    <t>2024-07-23</t>
+  </si>
+  <si>
+    <t>2024-08-01</t>
+  </si>
+  <si>
+    <t>Technology</t>
   </si>
   <si>
     <t>Financial Services</t>
   </si>
   <si>
-    <t>Technology</t>
-  </si>
-  <si>
-    <t>Consumer Cyclical</t>
-  </si>
-  <si>
-    <t>Utilities</t>
-  </si>
-  <si>
     <t>Industrials</t>
   </si>
   <si>
-    <t>Asset Management</t>
-  </si>
-  <si>
-    <t>Software - Application</t>
+    <t>Communication Services</t>
+  </si>
+  <si>
+    <t>Healthcare</t>
   </si>
   <si>
     <t>Software - Infrastructure</t>
   </si>
   <si>
-    <t>Travel Services</t>
+    <t>Insurance - Property &amp; Casualty</t>
   </si>
   <si>
     <t>Semiconductors</t>
   </si>
   <si>
-    <t>Internet Retail</t>
-  </si>
-  <si>
-    <t>Utilities - Independent Power Producers</t>
-  </si>
-  <si>
-    <t>Aerospace &amp; Defense</t>
+    <t>Engineering &amp; Construction</t>
+  </si>
+  <si>
+    <t>Railroads</t>
   </si>
   <si>
     <t>Specialty Industrial Machinery</t>
   </si>
   <si>
-    <t>Restaurants</t>
-  </si>
-  <si>
     <t>Computer Hardware</t>
+  </si>
+  <si>
+    <t>Internet Content &amp; Information</t>
+  </si>
+  <si>
+    <t>Medical Care Facilities</t>
   </si>
 </sst>
 </file>
@@ -632,7 +581,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AK20"/>
+  <dimension ref="A1:AK13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:37">
@@ -753,58 +702,58 @@
         <v>37</v>
       </c>
       <c r="B2">
-        <v>94.8</v>
+        <v>92.81437125748504</v>
       </c>
       <c r="C2">
-        <v>219</v>
+        <v>380</v>
       </c>
       <c r="D2">
-        <v>79.95999999999999</v>
+        <v>122.38</v>
       </c>
       <c r="E2">
-        <v>1.63</v>
+        <v>1.25</v>
       </c>
       <c r="F2">
-        <v>0.06534651992661855</v>
+        <v>-0.8630517841199804</v>
       </c>
       <c r="G2">
-        <v>2.11</v>
+        <v>1.36</v>
       </c>
       <c r="H2">
-        <v>0.1513780862229854</v>
+        <v>-0.5454802084808144</v>
       </c>
       <c r="I2">
-        <v>81.51799926757812</v>
+        <v>124.0740005493164</v>
       </c>
       <c r="J2">
-        <v>80.82049980163575</v>
+        <v>123.764001083374</v>
       </c>
       <c r="K2">
-        <v>71.03699974060059</v>
+        <v>119.1400010681152</v>
       </c>
       <c r="L2">
-        <v>60.19104995727539</v>
+        <v>95.49940013885498</v>
       </c>
       <c r="M2">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="N2">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="P2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>12.22222222222222</v>
+        <v>0</v>
       </c>
       <c r="U2" t="b">
         <v>1</v>
@@ -813,49 +762,49 @@
         <v>0</v>
       </c>
       <c r="W2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X2">
-        <v>47.01</v>
+        <v>67.43000000000001</v>
       </c>
       <c r="Y2">
-        <v>85.66</v>
+        <v>127.15</v>
       </c>
       <c r="Z2">
+        <v>16.08</v>
+      </c>
+      <c r="AA2">
+        <v>551.13</v>
+      </c>
+      <c r="AB2">
+        <v>266.4</v>
+      </c>
+      <c r="AC2">
+        <v>2325.81</v>
+      </c>
+      <c r="AD2">
+        <v>1791.15</v>
+      </c>
+      <c r="AE2">
+        <v>735.5599999999999</v>
+      </c>
+      <c r="AF2">
+        <v>66.67</v>
+      </c>
+      <c r="AG2">
+        <v>74.19</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>49</v>
+      </c>
+      <c r="AI2" t="s">
         <v>56</v>
       </c>
-      <c r="AA2">
-        <v>10.49</v>
-      </c>
-      <c r="AB2">
-        <v>1750</v>
-      </c>
-      <c r="AC2">
-        <v>533.33</v>
-      </c>
-      <c r="AD2">
-        <v>3.89</v>
-      </c>
-      <c r="AE2">
-        <v>74.48999999999999</v>
-      </c>
-      <c r="AF2">
-        <v>164.86</v>
-      </c>
-      <c r="AG2">
-        <v>37.04</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>57</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>71</v>
-      </c>
       <c r="AJ2" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="AK2">
-        <v>86.52833845284135</v>
+        <v>85.69475267104367</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -863,49 +812,49 @@
         <v>38</v>
       </c>
       <c r="B3">
-        <v>96.59999999999999</v>
+        <v>90.61876247504989</v>
       </c>
       <c r="C3">
-        <v>123</v>
+        <v>227</v>
       </c>
       <c r="D3">
-        <v>251.24</v>
+        <v>208.25</v>
       </c>
       <c r="E3">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="F3">
-        <v>-0.675897586703685</v>
+        <v>-0.9490880990478291</v>
       </c>
       <c r="G3">
-        <v>1.85</v>
+        <v>1.04</v>
       </c>
       <c r="H3">
-        <v>-0.3471604110713821</v>
+        <v>-0.8175118968660519</v>
       </c>
       <c r="I3">
-        <v>257.5860015869141</v>
+        <v>209.0440002441406</v>
       </c>
       <c r="J3">
-        <v>258.8055015563965</v>
+        <v>208.9629997253418</v>
       </c>
       <c r="K3">
-        <v>234.6806008911133</v>
+        <v>202.8286001586914</v>
       </c>
       <c r="L3">
-        <v>215.0737997436523</v>
+        <v>164.5680501174927</v>
       </c>
       <c r="M3">
         <v>1</v>
       </c>
       <c r="N3">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3">
         <v>0</v>
@@ -914,58 +863,58 @@
         <v>0</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.777777777777778</v>
       </c>
       <c r="U3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V3" t="b">
         <v>0</v>
       </c>
       <c r="W3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X3">
-        <v>134.24</v>
+        <v>111.41</v>
       </c>
       <c r="Y3">
-        <v>268.36</v>
+        <v>216.21</v>
       </c>
       <c r="Z3">
-        <v>197.01</v>
+        <v>121.47</v>
       </c>
       <c r="AA3">
-        <v>16.98</v>
+        <v>4.33</v>
       </c>
       <c r="AB3">
-        <v>1562.5</v>
+        <v>395.45</v>
       </c>
       <c r="AC3">
-        <v>1360</v>
+        <v>592.98</v>
       </c>
       <c r="AD3">
-        <v>2.11</v>
+        <v>10.69</v>
       </c>
       <c r="AE3">
-        <v>-3.08</v>
+        <v>16.52</v>
       </c>
       <c r="AF3">
-        <v>550</v>
+        <v>78.42</v>
       </c>
       <c r="AG3">
-        <v>300</v>
+        <v>233.33</v>
       </c>
       <c r="AH3" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="AI3" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="AJ3" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="AK3">
-        <v>82.64566073279751</v>
+        <v>85.20823064460365</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -973,109 +922,109 @@
         <v>39</v>
       </c>
       <c r="B4">
-        <v>97.59999999999999</v>
+        <v>99.60079840319361</v>
       </c>
       <c r="C4">
-        <v>107</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>141.65</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="E4">
-        <v>1.79</v>
+        <v>3.79</v>
       </c>
       <c r="F4">
-        <v>0.3618441625787404</v>
+        <v>1.868601214839211</v>
       </c>
       <c r="G4">
-        <v>2.2</v>
+        <v>3.68</v>
       </c>
       <c r="H4">
-        <v>0.3239491045171903</v>
+        <v>1.426749532312157</v>
       </c>
       <c r="I4">
-        <v>144.9149993896484</v>
+        <v>84.84060211181641</v>
       </c>
       <c r="J4">
-        <v>149.2134986877441</v>
+        <v>85.28354988098144</v>
       </c>
       <c r="K4">
-        <v>137.0112992858887</v>
+        <v>85.6636801147461</v>
       </c>
       <c r="L4">
-        <v>118.1441747283936</v>
+        <v>58.29821998596191</v>
       </c>
       <c r="M4">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="N4">
-        <v>1.06</v>
+        <v>0.99</v>
       </c>
       <c r="P4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T4">
-        <v>12.77777777777778</v>
+        <v>2.777777777777778</v>
       </c>
       <c r="U4" t="b">
         <v>0</v>
       </c>
       <c r="V4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W4" t="b">
         <v>1</v>
       </c>
       <c r="X4">
-        <v>66.11</v>
+        <v>27.24</v>
       </c>
       <c r="Y4">
-        <v>159</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="Z4">
-        <v>42.5</v>
+        <v>1534.48</v>
       </c>
       <c r="AA4">
-        <v>-315.95</v>
+        <v>691.4</v>
       </c>
       <c r="AB4">
-        <v>1105</v>
+        <v>365.25</v>
       </c>
       <c r="AC4">
-        <v>125</v>
+        <v>504.82</v>
       </c>
       <c r="AD4">
-        <v>8.949999999999999</v>
+        <v>28.59</v>
       </c>
       <c r="AE4">
-        <v>-16</v>
+        <v>35.68</v>
       </c>
       <c r="AF4">
-        <v>114.29</v>
+        <v>48</v>
       </c>
       <c r="AG4">
-        <v>25</v>
+        <v>201.2</v>
       </c>
       <c r="AH4" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="AI4" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="AJ4" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="AK4">
-        <v>71.18543227281737</v>
+        <v>83.28789004269656</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1083,40 +1032,40 @@
         <v>40</v>
       </c>
       <c r="B5">
-        <v>91.40000000000001</v>
+        <v>90.41916167664671</v>
       </c>
       <c r="C5">
-        <v>138</v>
+        <v>411</v>
       </c>
       <c r="D5">
-        <v>133.72</v>
+        <v>258.56</v>
       </c>
       <c r="E5">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="F5">
-        <v>0.1950642385869218</v>
+        <v>-0.5404156031405484</v>
       </c>
       <c r="G5">
-        <v>2.36</v>
+        <v>1.82</v>
       </c>
       <c r="H5">
-        <v>0.6307420259291084</v>
+        <v>-0.1544346564270356</v>
       </c>
       <c r="I5">
-        <v>134.9519989013672</v>
+        <v>258.1859985351563</v>
       </c>
       <c r="J5">
-        <v>140.3029998779297</v>
+        <v>254.5175010681152</v>
       </c>
       <c r="K5">
-        <v>130.2581999206543</v>
+        <v>247.8994000244141</v>
       </c>
       <c r="L5">
-        <v>127.7856751251221</v>
+        <v>208.0273502349854</v>
       </c>
       <c r="M5">
-        <v>0.96</v>
+        <v>1.01</v>
       </c>
       <c r="N5">
         <v>1.04</v>
@@ -1140,52 +1089,52 @@
         <v>0</v>
       </c>
       <c r="V5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W5" t="b">
         <v>1</v>
       </c>
       <c r="X5">
-        <v>84.79000000000001</v>
+        <v>153.74</v>
       </c>
       <c r="Y5">
-        <v>154.95</v>
+        <v>265.82</v>
       </c>
       <c r="Z5">
-        <v>90.56</v>
+        <v>32.12</v>
       </c>
       <c r="AA5">
-        <v>-624.91</v>
+        <v>13.57</v>
       </c>
       <c r="AB5">
-        <v>173.72</v>
+        <v>25.74</v>
       </c>
       <c r="AC5">
-        <v>1239.22</v>
+        <v>119.7</v>
       </c>
       <c r="AD5">
-        <v>47.94</v>
+        <v>3.4</v>
       </c>
       <c r="AE5">
-        <v>569.61</v>
+        <v>-22.87</v>
       </c>
       <c r="AF5">
-        <v>466.67</v>
+        <v>64.91</v>
       </c>
       <c r="AG5">
-        <v>-64.70999999999999</v>
+        <v>72.73</v>
       </c>
       <c r="AH5" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="AI5" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="AJ5" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="AK5">
-        <v>57.78840164093568</v>
+        <v>41.10821529811234</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1193,109 +1142,109 @@
         <v>41</v>
       </c>
       <c r="B6">
-        <v>99.8</v>
+        <v>93.61277445109781</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>275</v>
       </c>
       <c r="D6">
-        <v>48</v>
+        <v>161.08</v>
       </c>
       <c r="E6">
-        <v>1.7</v>
+        <v>2.45</v>
       </c>
       <c r="F6">
-        <v>0.1950642385869218</v>
+        <v>0.4274929397977479</v>
       </c>
       <c r="G6">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="H6">
-        <v>0.1322035286347409</v>
+        <v>-0.4009633740261571</v>
       </c>
       <c r="I6">
-        <v>48.55579986572265</v>
+        <v>163.0459991455078</v>
       </c>
       <c r="J6">
-        <v>48.31520004272461</v>
+        <v>150.8940002441406</v>
       </c>
       <c r="K6">
-        <v>47.03029998779297</v>
+        <v>145.2652001953125</v>
       </c>
       <c r="L6">
-        <v>40.93012491226196</v>
+        <v>123.5158000183105</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="N6">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="P6">
+        <v>2</v>
+      </c>
+      <c r="Q6">
         <v>5</v>
       </c>
-      <c r="Q6">
-        <v>0</v>
-      </c>
       <c r="R6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
       <c r="T6">
-        <v>7.222222222222221</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="U6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W6" t="b">
         <v>0</v>
       </c>
       <c r="X6">
-        <v>14.03</v>
+        <v>91.89</v>
       </c>
       <c r="Y6">
-        <v>50.55</v>
+        <v>167.49</v>
       </c>
       <c r="Z6">
-        <v>1017.05</v>
+        <v>25.81</v>
       </c>
       <c r="AA6">
-        <v>323.52</v>
+        <v>14.31</v>
       </c>
       <c r="AB6">
-        <v>157.09</v>
+        <v>10.3</v>
       </c>
       <c r="AC6">
-        <v>537.9299999999999</v>
+        <v>45.28</v>
       </c>
       <c r="AD6">
-        <v>27.79</v>
+        <v>2.64</v>
       </c>
       <c r="AE6">
-        <v>48</v>
+        <v>28.33</v>
       </c>
       <c r="AF6">
-        <v>201.2</v>
+        <v>-10.45</v>
       </c>
       <c r="AG6">
-        <v>43.1</v>
+        <v>26.42</v>
       </c>
       <c r="AH6" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="AI6" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="AJ6" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AK6">
-        <v>56.15845655525175</v>
+        <v>35.40210009656498</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1303,43 +1252,43 @@
         <v>42</v>
       </c>
       <c r="B7">
-        <v>94.59999999999999</v>
+        <v>94.61077844311377</v>
       </c>
       <c r="C7">
-        <v>6</v>
+        <v>462</v>
       </c>
       <c r="D7">
-        <v>144.57</v>
+        <v>544.91</v>
       </c>
       <c r="E7">
-        <v>1.31</v>
+        <v>1.1</v>
       </c>
       <c r="F7">
-        <v>-0.5276487653776242</v>
+        <v>-1.024369874609696</v>
       </c>
       <c r="G7">
-        <v>1.84</v>
+        <v>0.96</v>
       </c>
       <c r="H7">
-        <v>-0.3663349686596271</v>
+        <v>-0.8855198189623613</v>
       </c>
       <c r="I7">
-        <v>149.6580017089844</v>
+        <v>549.743994140625</v>
       </c>
       <c r="J7">
-        <v>150.0349998474121</v>
+        <v>550.4654998779297</v>
       </c>
       <c r="K7">
-        <v>144.3024005126953</v>
+        <v>543.7292004394532</v>
       </c>
       <c r="L7">
-        <v>128.465100402832</v>
+        <v>455.6309992980957</v>
       </c>
       <c r="M7">
         <v>1</v>
       </c>
       <c r="N7">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -1357,55 +1306,55 @@
         <v>0</v>
       </c>
       <c r="U7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W7" t="b">
         <v>0</v>
       </c>
       <c r="X7">
-        <v>81.43000000000001</v>
+        <v>318.32</v>
       </c>
       <c r="Y7">
-        <v>155.63</v>
+        <v>570.15</v>
       </c>
       <c r="Z7">
-        <v>1342.13</v>
+        <v>60.06</v>
       </c>
       <c r="AA7">
-        <v>26.04</v>
+        <v>2.14</v>
       </c>
       <c r="AB7">
-        <v>71.09999999999999</v>
+        <v>42.13</v>
       </c>
       <c r="AC7">
-        <v>3100</v>
+        <v>15.18</v>
       </c>
       <c r="AD7">
-        <v>5.4</v>
+        <v>6.03</v>
       </c>
       <c r="AE7">
-        <v>45.45</v>
+        <v>4.73</v>
       </c>
       <c r="AF7">
-        <v>112.9</v>
+        <v>-8.15</v>
       </c>
       <c r="AG7">
-        <v>933.33</v>
+        <v>19.74</v>
       </c>
       <c r="AH7" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="AI7" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="AJ7" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="AK7">
-        <v>54.82124900203854</v>
+        <v>33.1500318079142</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1413,43 +1362,43 @@
         <v>43</v>
       </c>
       <c r="B8">
-        <v>95</v>
+        <v>99.40119760479041</v>
       </c>
       <c r="C8">
-        <v>183</v>
+        <v>116</v>
       </c>
       <c r="D8">
-        <v>38.4</v>
+        <v>124.64</v>
       </c>
       <c r="E8">
-        <v>1.22</v>
+        <v>3.3</v>
       </c>
       <c r="F8">
-        <v>-0.6944286893694427</v>
+        <v>1.341628785906138</v>
       </c>
       <c r="G8">
-        <v>1.39</v>
+        <v>4.94</v>
       </c>
       <c r="H8">
-        <v>-1.229190060130649</v>
+        <v>2.49787430532903</v>
       </c>
       <c r="I8">
-        <v>38.39800033569336</v>
+        <v>124.5019989013672</v>
       </c>
       <c r="J8">
-        <v>37.76900024414063</v>
+        <v>122.7470008850098</v>
       </c>
       <c r="K8">
-        <v>35.8636003112793</v>
+        <v>113.6884001159668</v>
       </c>
       <c r="L8">
-        <v>29.63405010223389</v>
+        <v>80.49355020523072</v>
       </c>
       <c r="M8">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N8">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -1467,55 +1416,55 @@
         <v>0</v>
       </c>
       <c r="U8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8" t="b">
         <v>1</v>
       </c>
       <c r="W8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X8">
-        <v>21.18</v>
+        <v>43.39</v>
       </c>
       <c r="Y8">
-        <v>38.9</v>
+        <v>136.16</v>
       </c>
       <c r="Z8">
-        <v>12.35</v>
+        <v>61</v>
       </c>
       <c r="AA8">
-        <v>-31.62</v>
+        <v>-13.72</v>
       </c>
       <c r="AB8">
-        <v>285.16</v>
+        <v>7.73</v>
       </c>
       <c r="AC8">
-        <v>258.75</v>
+        <v>100</v>
       </c>
       <c r="AD8">
-        <v>14.26</v>
+        <v>-50.15</v>
       </c>
       <c r="AE8">
-        <v>7.63</v>
+        <v>16.55</v>
       </c>
       <c r="AF8">
-        <v>-31.4</v>
+        <v>117.19</v>
       </c>
       <c r="AG8">
-        <v>315</v>
+        <v>-20.99</v>
       </c>
       <c r="AH8" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="AI8" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="AJ8" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="AK8">
-        <v>51.63920838692619</v>
+        <v>27.70138957633599</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1523,109 +1472,109 @@
         <v>44</v>
       </c>
       <c r="B9">
-        <v>95.39999999999999</v>
+        <v>90.01996007984032</v>
       </c>
       <c r="C9">
-        <v>384</v>
+        <v>10</v>
       </c>
       <c r="D9">
-        <v>671.87</v>
+        <v>162.78</v>
       </c>
       <c r="E9">
-        <v>1.69</v>
+        <v>2.82</v>
       </c>
       <c r="F9">
-        <v>0.1765331359211642</v>
+        <v>0.825410896339047</v>
       </c>
       <c r="G9">
-        <v>1.72</v>
+        <v>2.1</v>
       </c>
       <c r="H9">
-        <v>-0.5964296597185663</v>
+        <v>0.08359307091004715</v>
       </c>
       <c r="I9">
-        <v>688.7280029296875</v>
+        <v>163.2019989013672</v>
       </c>
       <c r="J9">
-        <v>697.0514984130859</v>
+        <v>157.4029991149902</v>
       </c>
       <c r="K9">
-        <v>657.5941967773438</v>
+        <v>148.6014001464844</v>
       </c>
       <c r="L9">
-        <v>563.1176501464844</v>
+        <v>138.5745502853393</v>
       </c>
       <c r="M9">
-        <v>0.99</v>
+        <v>1.04</v>
       </c>
       <c r="N9">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="P9">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="Q9">
         <v>1</v>
       </c>
       <c r="R9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
       <c r="T9">
-        <v>8.333333333333332</v>
+        <v>2.777777777777778</v>
       </c>
       <c r="U9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W9" t="b">
         <v>0</v>
       </c>
       <c r="X9">
-        <v>353.62</v>
+        <v>103.71</v>
       </c>
       <c r="Y9">
-        <v>720.6799999999999</v>
+        <v>174.71</v>
       </c>
       <c r="Z9">
-        <v>115.3</v>
+        <v>2021.86</v>
       </c>
       <c r="AA9">
-        <v>-2701.39</v>
+        <v>17.63</v>
       </c>
       <c r="AB9">
-        <v>349.71</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="AC9">
-        <v>59.46</v>
+        <v>31.72</v>
       </c>
       <c r="AD9">
-        <v>3.37</v>
+        <v>8.08</v>
       </c>
       <c r="AE9">
-        <v>-76.95</v>
+        <v>15.76</v>
       </c>
       <c r="AF9">
-        <v>591.89</v>
+        <v>5.77</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>7.59</v>
       </c>
       <c r="AH9" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="AI9" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="AJ9" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="AK9">
-        <v>49.59683613952767</v>
+        <v>26.86978007024495</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1633,49 +1582,49 @@
         <v>45</v>
       </c>
       <c r="B10">
-        <v>99.2</v>
+        <v>90.21956087824351</v>
       </c>
       <c r="C10">
-        <v>163</v>
+        <v>13</v>
       </c>
       <c r="D10">
-        <v>119</v>
+        <v>164.64</v>
       </c>
       <c r="E10">
-        <v>2.46</v>
+        <v>2.75</v>
       </c>
       <c r="F10">
-        <v>1.603428041184499</v>
+        <v>0.7501291207771797</v>
       </c>
       <c r="G10">
-        <v>2.23</v>
+        <v>2.06</v>
       </c>
       <c r="H10">
-        <v>0.3814727772819247</v>
+        <v>0.04958910986189244</v>
       </c>
       <c r="I10">
-        <v>123.2100006103516</v>
+        <v>165.0559997558594</v>
       </c>
       <c r="J10">
-        <v>122.9645000457764</v>
+        <v>158.9855003356934</v>
       </c>
       <c r="K10">
-        <v>107.7854000854492</v>
+        <v>149.8883993530274</v>
       </c>
       <c r="L10">
-        <v>92.56399991989136</v>
+        <v>139.7381497955322</v>
       </c>
       <c r="M10">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="N10">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="P10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -1684,58 +1633,58 @@
         <v>0</v>
       </c>
       <c r="T10">
-        <v>2.777777777777778</v>
+        <v>2.222222222222222</v>
       </c>
       <c r="U10" t="b">
         <v>0</v>
       </c>
       <c r="V10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W10" t="b">
         <v>0</v>
       </c>
       <c r="X10">
-        <v>48.88</v>
+        <v>104.5</v>
       </c>
       <c r="Y10">
-        <v>130.97</v>
+        <v>176.42</v>
       </c>
       <c r="Z10">
-        <v>25.98</v>
+        <v>2039.67</v>
       </c>
       <c r="AA10">
-        <v>0.73</v>
+        <v>17.63</v>
       </c>
       <c r="AB10">
-        <v>126.01</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="AC10">
-        <v>302.05</v>
+        <v>31.72</v>
       </c>
       <c r="AD10">
-        <v>22</v>
+        <v>8.08</v>
       </c>
       <c r="AE10">
-        <v>120.11</v>
+        <v>15.76</v>
       </c>
       <c r="AF10">
-        <v>1042.11</v>
+        <v>5.77</v>
       </c>
       <c r="AG10">
-        <v>90.26000000000001</v>
+        <v>7.59</v>
       </c>
       <c r="AH10" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="AI10" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="AJ10" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="AK10">
-        <v>45.99811344525102</v>
+        <v>26.03644673691162</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -1743,109 +1692,109 @@
         <v>46</v>
       </c>
       <c r="B11">
-        <v>98.8</v>
+        <v>93.41317365269461</v>
       </c>
       <c r="C11">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="D11">
-        <v>245.65</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="E11">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="F11">
-        <v>-0.490586560046109</v>
+        <v>-0.8845608628519426</v>
       </c>
       <c r="G11">
-        <v>2.02</v>
+        <v>1.2</v>
       </c>
       <c r="H11">
-        <v>-0.02119293207121861</v>
+        <v>-0.6814960526734333</v>
       </c>
       <c r="I11">
-        <v>249.6700012207031</v>
+        <v>92.9479995727539</v>
       </c>
       <c r="J11">
-        <v>251.5514984130859</v>
+        <v>91.95649948120118</v>
       </c>
       <c r="K11">
-        <v>221.2260003662109</v>
+        <v>91.74699981689453</v>
       </c>
       <c r="L11">
-        <v>167.7890500640869</v>
+        <v>75.77019989013672</v>
       </c>
       <c r="M11">
-        <v>0.99</v>
+        <v>1.01</v>
       </c>
       <c r="N11">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="P11">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q11">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R11">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T11">
-        <v>12.22222222222222</v>
+        <v>0</v>
       </c>
       <c r="U11" t="b">
         <v>0</v>
       </c>
       <c r="V11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W11" t="b">
         <v>0</v>
       </c>
       <c r="X11">
-        <v>92.25</v>
+        <v>55.86</v>
       </c>
       <c r="Y11">
-        <v>261.81</v>
+        <v>96.17</v>
       </c>
       <c r="Z11">
-        <v>43.1</v>
+        <v>31.63</v>
       </c>
       <c r="AA11">
-        <v>0.1</v>
+        <v>15.58</v>
       </c>
       <c r="AB11">
-        <v>94.84999999999999</v>
+        <v>1.59</v>
       </c>
       <c r="AC11">
-        <v>155</v>
+        <v>42.5</v>
       </c>
       <c r="AD11">
-        <v>1.29</v>
+        <v>2.35</v>
       </c>
       <c r="AE11">
-        <v>175</v>
-      </c>
-      <c r="AF11" t="s">
-        <v>56</v>
+        <v>11.76</v>
+      </c>
+      <c r="AF11">
+        <v>15.91</v>
       </c>
       <c r="AG11">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="AH11" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="AI11" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="AJ11" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="AK11">
-        <v>45.36212434152558</v>
+        <v>8.890563675807467</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -1853,43 +1802,43 @@
         <v>47</v>
       </c>
       <c r="B12">
-        <v>97.8</v>
+        <v>97.0059880239521</v>
       </c>
       <c r="C12">
-        <v>12</v>
+        <v>184</v>
       </c>
       <c r="D12">
-        <v>16.85</v>
+        <v>318.26</v>
       </c>
       <c r="E12">
-        <v>3.33</v>
+        <v>1.77</v>
       </c>
       <c r="F12">
-        <v>3.21563397310541</v>
+        <v>-0.3038157370889649</v>
       </c>
       <c r="G12">
-        <v>3.07</v>
+        <v>1.34</v>
       </c>
       <c r="H12">
-        <v>1.992135614694498</v>
+        <v>-0.5624821890048918</v>
       </c>
       <c r="I12">
-        <v>17.54000053405762</v>
+        <v>320.9920043945312</v>
       </c>
       <c r="J12">
-        <v>18.1370002746582</v>
+        <v>317.0045013427734</v>
       </c>
       <c r="K12">
-        <v>15.31140014648438</v>
+        <v>305.8911981201172</v>
       </c>
       <c r="L12">
-        <v>14.09675003051758</v>
+        <v>246.603649597168</v>
       </c>
       <c r="M12">
-        <v>0.97</v>
+        <v>1.01</v>
       </c>
       <c r="N12">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -1898,64 +1847,64 @@
         <v>0</v>
       </c>
       <c r="R12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T12">
-        <v>9.444444444444446</v>
+        <v>0</v>
       </c>
       <c r="U12" t="b">
         <v>0</v>
       </c>
       <c r="V12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X12">
-        <v>7.98</v>
+        <v>165.24</v>
       </c>
       <c r="Y12">
-        <v>19.74</v>
+        <v>333.06</v>
       </c>
       <c r="Z12">
-        <v>19.01</v>
+        <v>125.67</v>
       </c>
       <c r="AA12">
-        <v>-0.05</v>
+        <v>3.96</v>
       </c>
       <c r="AB12">
-        <v>98.95</v>
+        <v>2.53</v>
       </c>
       <c r="AC12">
-        <v>92.73</v>
+        <v>10.22</v>
       </c>
       <c r="AD12">
-        <v>-0.71</v>
+        <v>4.25</v>
       </c>
       <c r="AE12">
-        <v>-104.71</v>
+        <v>-13.5</v>
       </c>
       <c r="AF12">
-        <v>365.62</v>
+        <v>6.28</v>
       </c>
       <c r="AG12">
-        <v>41.82</v>
+        <v>19.89</v>
       </c>
       <c r="AH12" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AI12" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="AJ12" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="AK12">
-        <v>39.87327624110723</v>
+        <v>3.385125253143263</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -1963,43 +1912,43 @@
         <v>48</v>
       </c>
       <c r="B13">
-        <v>91.60000000000001</v>
+        <v>91.21756487025948</v>
       </c>
       <c r="C13">
-        <v>310</v>
+        <v>447</v>
       </c>
       <c r="D13">
-        <v>267.08</v>
+        <v>139.01</v>
       </c>
       <c r="E13">
-        <v>1.18</v>
+        <v>1.45</v>
       </c>
       <c r="F13">
-        <v>-0.7685531000324731</v>
+        <v>-0.6479609968003591</v>
       </c>
       <c r="G13">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="H13">
-        <v>-0.2512876231301578</v>
+        <v>-0.0099178219723783</v>
       </c>
       <c r="I13">
-        <v>271.1819946289062</v>
+        <v>135.2339996337891</v>
       </c>
       <c r="J13">
-        <v>272.7029998779297</v>
+        <v>132.3724994659424</v>
       </c>
       <c r="K13">
-        <v>247.6182000732422</v>
+        <v>132.4546002197266</v>
       </c>
       <c r="L13">
-        <v>222.8400002288818</v>
+        <v>107.7911500167847</v>
       </c>
       <c r="M13">
-        <v>0.99</v>
+        <v>1.02</v>
       </c>
       <c r="N13">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -2017,825 +1966,55 @@
         <v>0</v>
       </c>
       <c r="U13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W13" t="b">
         <v>0</v>
       </c>
       <c r="X13">
-        <v>157.85</v>
+        <v>71.51000000000001</v>
       </c>
       <c r="Y13">
-        <v>279.83</v>
+        <v>141.54</v>
       </c>
       <c r="Z13">
-        <v>56.39</v>
+        <v>9.76</v>
       </c>
       <c r="AA13">
-        <v>-0.86</v>
+        <v>45.51</v>
       </c>
       <c r="AB13">
-        <v>113.87</v>
+        <v>4.24</v>
       </c>
       <c r="AC13">
-        <v>187.76</v>
+        <v>31.25</v>
       </c>
       <c r="AD13">
-        <v>1.72</v>
+        <v>18.53</v>
       </c>
       <c r="AE13">
-        <v>43.33</v>
-      </c>
-      <c r="AF13" t="s">
-        <v>56</v>
+        <v>-37.78</v>
+      </c>
+      <c r="AF13">
+        <v>37.76</v>
       </c>
       <c r="AG13">
-        <v>100</v>
+        <v>53.12</v>
       </c>
       <c r="AH13" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="AI13" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="AJ13" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="AK13">
-        <v>39.20641251884967</v>
-      </c>
-    </row>
-    <row r="14" spans="1:37">
-      <c r="A14" t="s">
-        <v>49</v>
-      </c>
-      <c r="B14">
-        <v>94</v>
-      </c>
-      <c r="C14">
-        <v>485</v>
-      </c>
-      <c r="D14">
-        <v>3419.94</v>
-      </c>
-      <c r="E14">
-        <v>1.27</v>
-      </c>
-      <c r="F14">
-        <v>-0.6017731760406546</v>
-      </c>
-      <c r="G14">
-        <v>1.47</v>
-      </c>
-      <c r="H14">
-        <v>-1.075793599424689</v>
-      </c>
-      <c r="I14">
-        <v>3481.4919921875</v>
-      </c>
-      <c r="J14">
-        <v>3438.757495117187</v>
-      </c>
-      <c r="K14">
-        <v>3184.696401367188</v>
-      </c>
-      <c r="L14">
-        <v>2921.753098144531</v>
-      </c>
-      <c r="M14">
-        <v>1.01</v>
-      </c>
-      <c r="N14">
-        <v>1.09</v>
-      </c>
-      <c r="P14">
-        <v>7</v>
-      </c>
-      <c r="Q14">
-        <v>2</v>
-      </c>
-      <c r="R14">
-        <v>0</v>
-      </c>
-      <c r="S14">
-        <v>0</v>
-      </c>
-      <c r="T14">
-        <v>6.11111111111111</v>
-      </c>
-      <c r="U14" t="b">
-        <v>1</v>
-      </c>
-      <c r="V14" t="b">
-        <v>0</v>
-      </c>
-      <c r="W14" t="b">
-        <v>1</v>
-      </c>
-      <c r="X14">
-        <v>2056.78</v>
-      </c>
-      <c r="Y14">
-        <v>3580.62</v>
-      </c>
-      <c r="Z14">
-        <v>110.98</v>
-      </c>
-      <c r="AA14">
-        <v>0.54</v>
-      </c>
-      <c r="AB14">
-        <v>56.24</v>
-      </c>
-      <c r="AC14">
-        <v>131.16</v>
-      </c>
-      <c r="AD14">
-        <v>-401.76</v>
-      </c>
-      <c r="AE14">
-        <v>100.85</v>
-      </c>
-      <c r="AF14">
-        <v>397.31</v>
-      </c>
-      <c r="AG14">
-        <v>-76.86</v>
-      </c>
-      <c r="AH14" t="s">
-        <v>67</v>
-      </c>
-      <c r="AI14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AJ14" t="s">
-        <v>79</v>
-      </c>
-      <c r="AK14">
-        <v>33.66460599456133</v>
-      </c>
-    </row>
-    <row r="15" spans="1:37">
-      <c r="A15" t="s">
-        <v>50</v>
-      </c>
-      <c r="B15">
-        <v>91.2</v>
-      </c>
-      <c r="C15">
-        <v>490</v>
-      </c>
-      <c r="D15">
-        <v>975.53</v>
-      </c>
-      <c r="E15">
-        <v>1.16</v>
-      </c>
-      <c r="F15">
-        <v>-0.8056153053639883</v>
-      </c>
-      <c r="G15">
-        <v>1.67</v>
-      </c>
-      <c r="H15">
-        <v>-0.692302447659791</v>
-      </c>
-      <c r="I15">
-        <v>992.94599609375</v>
-      </c>
-      <c r="J15">
-        <v>992.1700012207032</v>
-      </c>
-      <c r="K15">
-        <v>950.9322033691407</v>
-      </c>
-      <c r="L15">
-        <v>859.1522512817382</v>
-      </c>
-      <c r="M15">
-        <v>1</v>
-      </c>
-      <c r="N15">
-        <v>1.04</v>
-      </c>
-      <c r="P15">
-        <v>2</v>
-      </c>
-      <c r="Q15">
-        <v>3</v>
-      </c>
-      <c r="R15">
-        <v>0</v>
-      </c>
-      <c r="S15">
-        <v>4</v>
-      </c>
-      <c r="T15">
-        <v>11.11111111111111</v>
-      </c>
-      <c r="U15" t="b">
-        <v>1</v>
-      </c>
-      <c r="V15" t="b">
-        <v>0</v>
-      </c>
-      <c r="W15" t="b">
-        <v>0</v>
-      </c>
-      <c r="X15">
-        <v>627.15</v>
-      </c>
-      <c r="Y15">
-        <v>1018.5</v>
-      </c>
-      <c r="Z15">
-        <v>48.23</v>
-      </c>
-      <c r="AA15">
-        <v>1.19</v>
-      </c>
-      <c r="AB15">
-        <v>31.68</v>
-      </c>
-      <c r="AC15">
-        <v>117.42</v>
-      </c>
-      <c r="AD15">
-        <v>-20.93</v>
-      </c>
-      <c r="AE15">
-        <v>17.92</v>
-      </c>
-      <c r="AF15">
-        <v>15.41</v>
-      </c>
-      <c r="AG15">
-        <v>59.76</v>
-      </c>
-      <c r="AH15" t="s">
-        <v>68</v>
-      </c>
-      <c r="AI15" t="s">
-        <v>75</v>
-      </c>
-      <c r="AJ15" t="s">
-        <v>83</v>
-      </c>
-      <c r="AK15">
-        <v>30.58260018808637</v>
-      </c>
-    </row>
-    <row r="16" spans="1:37">
-      <c r="A16" t="s">
-        <v>51</v>
-      </c>
-      <c r="B16">
-        <v>93.60000000000001</v>
-      </c>
-      <c r="C16">
-        <v>203</v>
-      </c>
-      <c r="D16">
-        <v>144.82</v>
-      </c>
-      <c r="E16">
-        <v>1.84</v>
-      </c>
-      <c r="F16">
-        <v>0.4544996759075284</v>
-      </c>
-      <c r="G16">
-        <v>3.23</v>
-      </c>
-      <c r="H16">
-        <v>2.298928536106417</v>
-      </c>
-      <c r="I16">
-        <v>148.7279998779297</v>
-      </c>
-      <c r="J16">
-        <v>148.3700004577637</v>
-      </c>
-      <c r="K16">
-        <v>131.2097998046875</v>
-      </c>
-      <c r="L16">
-        <v>110.1466999816895</v>
-      </c>
-      <c r="M16">
-        <v>1</v>
-      </c>
-      <c r="N16">
-        <v>1.13</v>
-      </c>
-      <c r="P16">
-        <v>0</v>
-      </c>
-      <c r="Q16">
-        <v>1</v>
-      </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
-      <c r="S16">
-        <v>0</v>
-      </c>
-      <c r="T16">
-        <v>1.111111111111111</v>
-      </c>
-      <c r="U16" t="b">
-        <v>0</v>
-      </c>
-      <c r="V16" t="b">
-        <v>0</v>
-      </c>
-      <c r="W16" t="b">
-        <v>0</v>
-      </c>
-      <c r="X16">
-        <v>87.94</v>
-      </c>
-      <c r="Y16">
-        <v>155.84</v>
-      </c>
-      <c r="Z16">
-        <v>15.23</v>
-      </c>
-      <c r="AA16">
-        <v>12.21</v>
-      </c>
-      <c r="AB16">
-        <v>36.88</v>
-      </c>
-      <c r="AC16">
-        <v>161.4</v>
-      </c>
-      <c r="AD16">
-        <v>10.42</v>
-      </c>
-      <c r="AE16">
-        <v>13.74</v>
-      </c>
-      <c r="AF16">
-        <v>375.79</v>
-      </c>
-      <c r="AG16">
-        <v>-183.33</v>
-      </c>
-      <c r="AH16" t="s">
-        <v>68</v>
-      </c>
-      <c r="AI16" t="s">
-        <v>73</v>
-      </c>
-      <c r="AJ16" t="s">
-        <v>79</v>
-      </c>
-      <c r="AK16">
-        <v>26.72639337933549</v>
-      </c>
-    </row>
-    <row r="17" spans="1:37">
-      <c r="A17" t="s">
-        <v>52</v>
-      </c>
-      <c r="B17">
-        <v>90.8</v>
-      </c>
-      <c r="C17">
-        <v>447</v>
-      </c>
-      <c r="D17">
-        <v>452.06</v>
-      </c>
-      <c r="E17">
-        <v>1.14</v>
-      </c>
-      <c r="F17">
-        <v>-0.8426775106955036</v>
-      </c>
-      <c r="G17">
-        <v>1.82</v>
-      </c>
-      <c r="H17">
-        <v>-0.4046840838361169</v>
-      </c>
-      <c r="I17">
-        <v>456.8019958496094</v>
-      </c>
-      <c r="J17">
-        <v>451.0649993896484</v>
-      </c>
-      <c r="K17">
-        <v>427.3375994873047</v>
-      </c>
-      <c r="L17">
-        <v>384.1872999572754</v>
-      </c>
-      <c r="M17">
-        <v>1.01</v>
-      </c>
-      <c r="N17">
-        <v>1.07</v>
-      </c>
-      <c r="P17">
-        <v>0</v>
-      </c>
-      <c r="Q17">
-        <v>0</v>
-      </c>
-      <c r="R17">
-        <v>0</v>
-      </c>
-      <c r="S17">
-        <v>0</v>
-      </c>
-      <c r="T17">
-        <v>0</v>
-      </c>
-      <c r="U17" t="b">
-        <v>1</v>
-      </c>
-      <c r="V17" t="b">
-        <v>0</v>
-      </c>
-      <c r="W17" t="b">
-        <v>0</v>
-      </c>
-      <c r="X17">
-        <v>291.62</v>
-      </c>
-      <c r="Y17">
-        <v>464</v>
-      </c>
-      <c r="Z17">
-        <v>50.78</v>
-      </c>
-      <c r="AA17">
-        <v>2.98</v>
-      </c>
-      <c r="AB17">
-        <v>42.37</v>
-      </c>
-      <c r="AC17">
-        <v>64.61</v>
-      </c>
-      <c r="AD17">
-        <v>6.16</v>
-      </c>
-      <c r="AE17">
-        <v>-8.15</v>
-      </c>
-      <c r="AF17">
-        <v>19.74</v>
-      </c>
-      <c r="AG17">
-        <v>49.68</v>
-      </c>
-      <c r="AH17" t="s">
-        <v>62</v>
-      </c>
-      <c r="AI17" t="s">
-        <v>75</v>
-      </c>
-      <c r="AJ17" t="s">
-        <v>84</v>
-      </c>
-      <c r="AK17">
-        <v>20.63007608810392</v>
-      </c>
-    </row>
-    <row r="18" spans="1:37">
-      <c r="A18" t="s">
-        <v>53</v>
-      </c>
-      <c r="B18">
-        <v>93</v>
-      </c>
-      <c r="C18">
-        <v>52</v>
-      </c>
-      <c r="D18">
-        <v>44.41</v>
-      </c>
-      <c r="E18">
-        <v>1.18</v>
-      </c>
-      <c r="F18">
-        <v>-0.7685531000324731</v>
-      </c>
-      <c r="G18">
-        <v>1.22</v>
-      </c>
-      <c r="H18">
-        <v>-1.555157539130812</v>
-      </c>
-      <c r="I18">
-        <v>45.05684051513672</v>
-      </c>
-      <c r="J18">
-        <v>45.62284030914306</v>
-      </c>
-      <c r="K18">
-        <v>43.3913720703125</v>
-      </c>
-      <c r="L18">
-        <v>39.80558303833008</v>
-      </c>
-      <c r="M18">
-        <v>0.99</v>
-      </c>
-      <c r="N18">
-        <v>1.04</v>
-      </c>
-      <c r="P18">
-        <v>8</v>
-      </c>
-      <c r="Q18">
-        <v>0</v>
-      </c>
-      <c r="R18">
-        <v>1</v>
-      </c>
-      <c r="S18">
-        <v>0</v>
-      </c>
-      <c r="T18">
-        <v>5.555555555555555</v>
-      </c>
-      <c r="U18" t="b">
-        <v>1</v>
-      </c>
-      <c r="V18" t="b">
-        <v>0</v>
-      </c>
-      <c r="W18" t="b">
-        <v>0</v>
-      </c>
-      <c r="X18">
-        <v>26.88</v>
-      </c>
-      <c r="Y18">
-        <v>46.97</v>
-      </c>
-      <c r="Z18">
-        <v>50.71</v>
-      </c>
-      <c r="AA18">
-        <v>679.46</v>
-      </c>
-      <c r="AB18">
-        <v>15.1</v>
-      </c>
-      <c r="AC18">
-        <v>42.68</v>
-      </c>
-      <c r="AD18">
-        <v>10.85</v>
-      </c>
-      <c r="AE18">
-        <v>-8</v>
-      </c>
-      <c r="AF18">
-        <v>18.37</v>
-      </c>
-      <c r="AG18">
-        <v>31.02</v>
-      </c>
-      <c r="AH18" t="s">
-        <v>57</v>
-      </c>
-      <c r="AI18" t="s">
-        <v>73</v>
-      </c>
-      <c r="AJ18" t="s">
-        <v>85</v>
-      </c>
-      <c r="AK18">
-        <v>11.03330899572033</v>
-      </c>
-    </row>
-    <row r="19" spans="1:37">
-      <c r="A19" t="s">
-        <v>54</v>
-      </c>
-      <c r="B19">
-        <v>96.2</v>
-      </c>
-      <c r="C19">
-        <v>171</v>
-      </c>
-      <c r="D19">
-        <v>75.97</v>
-      </c>
-      <c r="E19">
-        <v>1.77</v>
-      </c>
-      <c r="F19">
-        <v>0.3247819572472251</v>
-      </c>
-      <c r="G19">
-        <v>1.75</v>
-      </c>
-      <c r="H19">
-        <v>-0.5389059869538315</v>
-      </c>
-      <c r="I19">
-        <v>76.10800018310547</v>
-      </c>
-      <c r="J19">
-        <v>73.16099967956544</v>
-      </c>
-      <c r="K19">
-        <v>72.03440002441407</v>
-      </c>
-      <c r="L19">
-        <v>58.17235008239746</v>
-      </c>
-      <c r="M19">
-        <v>1.04</v>
-      </c>
-      <c r="N19">
-        <v>1.06</v>
-      </c>
-      <c r="P19">
-        <v>0</v>
-      </c>
-      <c r="Q19">
-        <v>0</v>
-      </c>
-      <c r="R19">
-        <v>0</v>
-      </c>
-      <c r="S19">
-        <v>0</v>
-      </c>
-      <c r="T19">
-        <v>0</v>
-      </c>
-      <c r="U19" t="b">
-        <v>0</v>
-      </c>
-      <c r="V19" t="b">
-        <v>1</v>
-      </c>
-      <c r="W19" t="b">
-        <v>1</v>
-      </c>
-      <c r="X19">
-        <v>35.96</v>
-      </c>
-      <c r="Y19">
-        <v>77.45</v>
-      </c>
-      <c r="Z19">
-        <v>49.51</v>
-      </c>
-      <c r="AA19">
-        <v>-7.74</v>
-      </c>
-      <c r="AB19">
-        <v>10.95</v>
-      </c>
-      <c r="AC19">
-        <v>57.95</v>
-      </c>
-      <c r="AD19">
-        <v>-39.07</v>
-      </c>
-      <c r="AE19">
-        <v>117.19</v>
-      </c>
-      <c r="AF19">
-        <v>-20.99</v>
-      </c>
-      <c r="AG19">
-        <v>-7.95</v>
-      </c>
-      <c r="AH19" t="s">
-        <v>69</v>
-      </c>
-      <c r="AI19" t="s">
-        <v>72</v>
-      </c>
-      <c r="AJ19" t="s">
-        <v>86</v>
-      </c>
-      <c r="AK19">
-        <v>5.620752022173512</v>
-      </c>
-    </row>
-    <row r="20" spans="1:37">
-      <c r="A20" t="s">
-        <v>55</v>
-      </c>
-      <c r="B20">
-        <v>97.39999999999999</v>
-      </c>
-      <c r="C20">
-        <v>117</v>
-      </c>
-      <c r="D20">
-        <v>57.64</v>
-      </c>
-      <c r="E20">
-        <v>1.37</v>
-      </c>
-      <c r="F20">
-        <v>-0.4164621493830785</v>
-      </c>
-      <c r="G20">
-        <v>2.64</v>
-      </c>
-      <c r="H20">
-        <v>1.167629638399967</v>
-      </c>
-      <c r="I20">
-        <v>58.19999923706055</v>
-      </c>
-      <c r="J20">
-        <v>57.83574962615967</v>
-      </c>
-      <c r="K20">
-        <v>54.35155006408691</v>
-      </c>
-      <c r="L20">
-        <v>45.29663747787475</v>
-      </c>
-      <c r="M20">
-        <v>1.01</v>
-      </c>
-      <c r="N20">
-        <v>1.07</v>
-      </c>
-      <c r="P20">
-        <v>0</v>
-      </c>
-      <c r="Q20">
-        <v>0</v>
-      </c>
-      <c r="R20">
-        <v>0</v>
-      </c>
-      <c r="S20">
-        <v>0</v>
-      </c>
-      <c r="T20">
-        <v>0</v>
-      </c>
-      <c r="U20" t="b">
-        <v>1</v>
-      </c>
-      <c r="V20" t="b">
-        <v>0</v>
-      </c>
-      <c r="W20" t="b">
-        <v>1</v>
-      </c>
-      <c r="X20">
-        <v>27.23</v>
-      </c>
-      <c r="Y20">
-        <v>60.17</v>
-      </c>
-      <c r="Z20">
-        <v>14.61</v>
-      </c>
-      <c r="AA20">
-        <v>58.19</v>
-      </c>
-      <c r="AB20">
-        <v>18.69</v>
-      </c>
-      <c r="AC20">
-        <v>26.62</v>
-      </c>
-      <c r="AD20">
-        <v>8.380000000000001</v>
-      </c>
-      <c r="AE20">
-        <v>10.69</v>
-      </c>
-      <c r="AF20">
-        <v>11.97</v>
-      </c>
-      <c r="AG20">
-        <v>2.16</v>
-      </c>
-      <c r="AH20" t="s">
-        <v>70</v>
-      </c>
-      <c r="AI20" t="s">
-        <v>72</v>
-      </c>
-      <c r="AJ20" t="s">
-        <v>86</v>
-      </c>
-      <c r="AK20">
-        <v>5.507262172816827</v>
+        <v>14.6309353341462</v>
       </c>
     </row>
   </sheetData>
